--- a/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -716,22 +716,22 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>126500</v>
+        <v>124800</v>
       </c>
       <c r="E8" s="3">
-        <v>87000</v>
+        <v>85900</v>
       </c>
       <c r="F8" s="3">
-        <v>69300</v>
+        <v>68400</v>
       </c>
       <c r="G8" s="3">
-        <v>39700</v>
+        <v>39200</v>
       </c>
       <c r="H8" s="3">
         <v>1100</v>
       </c>
       <c r="I8" s="3">
-        <v>16000</v>
+        <v>15800</v>
       </c>
       <c r="J8" s="3">
         <v>1600</v>
@@ -749,22 +749,22 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>59200</v>
+        <v>58400</v>
       </c>
       <c r="E9" s="3">
-        <v>44800</v>
+        <v>44200</v>
       </c>
       <c r="F9" s="3">
-        <v>39100</v>
+        <v>38600</v>
       </c>
       <c r="G9" s="3">
-        <v>21700</v>
+        <v>21400</v>
       </c>
       <c r="H9" s="3">
         <v>600</v>
       </c>
       <c r="I9" s="3">
-        <v>8500</v>
+        <v>8400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>5</v>
@@ -782,22 +782,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>67300</v>
+        <v>66400</v>
       </c>
       <c r="E10" s="3">
-        <v>42300</v>
+        <v>41700</v>
       </c>
       <c r="F10" s="3">
-        <v>30100</v>
+        <v>29700</v>
       </c>
       <c r="G10" s="3">
-        <v>18000</v>
+        <v>17700</v>
       </c>
       <c r="H10" s="3">
         <v>500</v>
       </c>
       <c r="I10" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>5</v>
@@ -902,16 +902,16 @@
         <v>2000</v>
       </c>
       <c r="F14" s="3">
-        <v>17100</v>
+        <v>16900</v>
       </c>
       <c r="G14" s="3">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="H14" s="3">
-        <v>16400</v>
+        <v>16200</v>
       </c>
       <c r="I14" s="3">
-        <v>18900</v>
+        <v>18700</v>
       </c>
       <c r="J14" s="3">
         <v>1800</v>
@@ -929,13 +929,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12600</v>
+        <v>12400</v>
       </c>
       <c r="E15" s="3">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="F15" s="3">
-        <v>4300</v>
+        <v>4200</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>5</v>
@@ -974,25 +974,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>127700</v>
+        <v>126000</v>
       </c>
       <c r="E17" s="3">
-        <v>96700</v>
+        <v>95400</v>
       </c>
       <c r="F17" s="3">
-        <v>87000</v>
+        <v>85900</v>
       </c>
       <c r="G17" s="3">
-        <v>51700</v>
+        <v>51100</v>
       </c>
       <c r="H17" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="I17" s="3">
-        <v>49100</v>
+        <v>48500</v>
       </c>
       <c r="J17" s="3">
-        <v>7500</v>
+        <v>7400</v>
       </c>
       <c r="K17" s="3">
         <v>9400</v>
@@ -1010,22 +1010,22 @@
         <v>-1200</v>
       </c>
       <c r="E18" s="3">
-        <v>-9700</v>
+        <v>-9600</v>
       </c>
       <c r="F18" s="3">
-        <v>-17800</v>
+        <v>-17500</v>
       </c>
       <c r="G18" s="3">
-        <v>-12100</v>
+        <v>-11900</v>
       </c>
       <c r="H18" s="3">
-        <v>-7100</v>
+        <v>-7000</v>
       </c>
       <c r="I18" s="3">
-        <v>-33200</v>
+        <v>-32700</v>
       </c>
       <c r="J18" s="3">
-        <v>-5900</v>
+        <v>-5800</v>
       </c>
       <c r="K18" s="3">
         <v>-7400</v>
@@ -1064,7 +1064,7 @@
         <v>-1500</v>
       </c>
       <c r="G20" s="3">
-        <v>-2600</v>
+        <v>-2500</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1091,19 +1091,19 @@
         <v>11100</v>
       </c>
       <c r="E21" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="F21" s="3">
-        <v>-15000</v>
+        <v>-14800</v>
       </c>
       <c r="G21" s="3">
-        <v>-11500</v>
+        <v>-11400</v>
       </c>
       <c r="H21" s="3">
-        <v>-6300</v>
+        <v>-6200</v>
       </c>
       <c r="I21" s="3">
-        <v>-32300</v>
+        <v>-31900</v>
       </c>
       <c r="J21" s="3">
         <v>-5300</v>
@@ -1154,25 +1154,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2900</v>
+        <v>-2800</v>
       </c>
       <c r="E23" s="3">
-        <v>-10000</v>
+        <v>-9800</v>
       </c>
       <c r="F23" s="3">
-        <v>-19800</v>
+        <v>-19600</v>
       </c>
       <c r="G23" s="3">
-        <v>-14700</v>
+        <v>-14500</v>
       </c>
       <c r="H23" s="3">
-        <v>-7100</v>
+        <v>-7000</v>
       </c>
       <c r="I23" s="3">
-        <v>-33500</v>
+        <v>-33100</v>
       </c>
       <c r="J23" s="3">
-        <v>-6000</v>
+        <v>-5900</v>
       </c>
       <c r="K23" s="3">
         <v>-7300</v>
@@ -1253,25 +1253,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="E26" s="3">
-        <v>-11200</v>
+        <v>-11100</v>
       </c>
       <c r="F26" s="3">
-        <v>-21600</v>
+        <v>-21300</v>
       </c>
       <c r="G26" s="3">
-        <v>-15500</v>
+        <v>-15300</v>
       </c>
       <c r="H26" s="3">
-        <v>-7100</v>
+        <v>-7000</v>
       </c>
       <c r="I26" s="3">
-        <v>-33500</v>
+        <v>-33100</v>
       </c>
       <c r="J26" s="3">
-        <v>-6000</v>
+        <v>-5900</v>
       </c>
       <c r="K26" s="3">
         <v>-7300</v>
@@ -1286,25 +1286,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="E27" s="3">
-        <v>-11200</v>
+        <v>-11100</v>
       </c>
       <c r="F27" s="3">
-        <v>-21600</v>
+        <v>-21300</v>
       </c>
       <c r="G27" s="3">
-        <v>-15500</v>
+        <v>-15300</v>
       </c>
       <c r="H27" s="3">
-        <v>-7100</v>
+        <v>-7000</v>
       </c>
       <c r="I27" s="3">
-        <v>-33500</v>
+        <v>-33100</v>
       </c>
       <c r="J27" s="3">
-        <v>-6000</v>
+        <v>-5900</v>
       </c>
       <c r="K27" s="3">
         <v>-7300</v>
@@ -1364,7 +1364,7 @@
         <v>-2300</v>
       </c>
       <c r="H29" s="3">
-        <v>-13600</v>
+        <v>-13400</v>
       </c>
       <c r="I29" s="3">
         <v>100</v>
@@ -1460,7 +1460,7 @@
         <v>1500</v>
       </c>
       <c r="G32" s="3">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1484,25 +1484,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="E33" s="3">
-        <v>-11200</v>
+        <v>-11100</v>
       </c>
       <c r="F33" s="3">
-        <v>-21700</v>
+        <v>-21400</v>
       </c>
       <c r="G33" s="3">
-        <v>-17800</v>
+        <v>-17600</v>
       </c>
       <c r="H33" s="3">
-        <v>-20700</v>
+        <v>-20400</v>
       </c>
       <c r="I33" s="3">
-        <v>-33400</v>
+        <v>-33000</v>
       </c>
       <c r="J33" s="3">
-        <v>-6000</v>
+        <v>-5900</v>
       </c>
       <c r="K33" s="3">
         <v>-7300</v>
@@ -1550,25 +1550,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="E35" s="3">
-        <v>-11200</v>
+        <v>-11100</v>
       </c>
       <c r="F35" s="3">
-        <v>-21700</v>
+        <v>-21400</v>
       </c>
       <c r="G35" s="3">
-        <v>-17800</v>
+        <v>-17600</v>
       </c>
       <c r="H35" s="3">
-        <v>-20700</v>
+        <v>-20400</v>
       </c>
       <c r="I35" s="3">
-        <v>-33400</v>
+        <v>-33000</v>
       </c>
       <c r="J35" s="3">
-        <v>-6000</v>
+        <v>-5900</v>
       </c>
       <c r="K35" s="3">
         <v>-7300</v>
@@ -1651,25 +1651,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16800</v>
+        <v>16600</v>
       </c>
       <c r="E41" s="3">
-        <v>23900</v>
+        <v>23600</v>
       </c>
       <c r="F41" s="3">
-        <v>39000</v>
+        <v>38400</v>
       </c>
       <c r="G41" s="3">
         <v>1000</v>
       </c>
       <c r="H41" s="3">
-        <v>21000</v>
+        <v>20700</v>
       </c>
       <c r="I41" s="3">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="J41" s="3">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="K41" s="3">
         <v>1300</v>
@@ -1717,22 +1717,22 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>24800</v>
+        <v>24500</v>
       </c>
       <c r="E43" s="3">
-        <v>12700</v>
+        <v>12500</v>
       </c>
       <c r="F43" s="3">
-        <v>15600</v>
+        <v>15400</v>
       </c>
       <c r="G43" s="3">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="H43" s="3">
-        <v>15700</v>
+        <v>15500</v>
       </c>
       <c r="I43" s="3">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -1795,7 +1795,7 @@
         <v>2200</v>
       </c>
       <c r="H45" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="I45" s="3">
         <v>1000</v>
@@ -1816,25 +1816,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>44400</v>
+        <v>43800</v>
       </c>
       <c r="E46" s="3">
-        <v>40200</v>
+        <v>39700</v>
       </c>
       <c r="F46" s="3">
-        <v>54900</v>
+        <v>54200</v>
       </c>
       <c r="G46" s="3">
-        <v>12400</v>
+        <v>12300</v>
       </c>
       <c r="H46" s="3">
-        <v>14600</v>
+        <v>14400</v>
       </c>
       <c r="I46" s="3">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="J46" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="K46" s="3">
         <v>2200</v>
@@ -1888,7 +1888,7 @@
         <v>1200</v>
       </c>
       <c r="F48" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="G48" s="3">
         <v>1500</v>
@@ -1915,22 +1915,22 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>98600</v>
+        <v>97300</v>
       </c>
       <c r="E49" s="3">
-        <v>77300</v>
+        <v>76300</v>
       </c>
       <c r="F49" s="3">
-        <v>47400</v>
+        <v>46700</v>
       </c>
       <c r="G49" s="3">
-        <v>51500</v>
+        <v>50800</v>
       </c>
       <c r="H49" s="3">
-        <v>52500</v>
+        <v>51800</v>
       </c>
       <c r="I49" s="3">
-        <v>10300</v>
+        <v>10100</v>
       </c>
       <c r="J49" s="3">
         <v>100</v>
@@ -2014,10 +2014,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11000</v>
+        <v>10800</v>
       </c>
       <c r="E52" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="F52" s="3">
         <v>3700</v>
@@ -2080,25 +2080,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>155800</v>
+        <v>153700</v>
       </c>
       <c r="E54" s="3">
-        <v>124500</v>
+        <v>122800</v>
       </c>
       <c r="F54" s="3">
-        <v>107600</v>
+        <v>106200</v>
       </c>
       <c r="G54" s="3">
-        <v>65500</v>
+        <v>64600</v>
       </c>
       <c r="H54" s="3">
-        <v>67600</v>
+        <v>66700</v>
       </c>
       <c r="I54" s="3">
-        <v>15500</v>
+        <v>15300</v>
       </c>
       <c r="J54" s="3">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="K54" s="3">
         <v>4700</v>
@@ -2143,19 +2143,19 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="E57" s="3">
         <v>2200</v>
       </c>
       <c r="F57" s="3">
-        <v>9600</v>
+        <v>9400</v>
       </c>
       <c r="G57" s="3">
-        <v>13200</v>
+        <v>13000</v>
       </c>
       <c r="H57" s="3">
-        <v>11900</v>
+        <v>11800</v>
       </c>
       <c r="I57" s="3">
         <v>5000</v>
@@ -2209,19 +2209,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>29200</v>
+        <v>28800</v>
       </c>
       <c r="E59" s="3">
-        <v>20500</v>
+        <v>20200</v>
       </c>
       <c r="F59" s="3">
-        <v>35100</v>
+        <v>34600</v>
       </c>
       <c r="G59" s="3">
-        <v>17500</v>
+        <v>17300</v>
       </c>
       <c r="H59" s="3">
-        <v>7600</v>
+        <v>7500</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
@@ -2242,19 +2242,19 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>36300</v>
+        <v>35800</v>
       </c>
       <c r="E60" s="3">
-        <v>22900</v>
+        <v>22600</v>
       </c>
       <c r="F60" s="3">
-        <v>44800</v>
+        <v>44200</v>
       </c>
       <c r="G60" s="3">
-        <v>31000</v>
+        <v>30600</v>
       </c>
       <c r="H60" s="3">
-        <v>15100</v>
+        <v>14900</v>
       </c>
       <c r="I60" s="3">
         <v>1900</v>
@@ -2275,7 +2275,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10400</v>
+        <v>10300</v>
       </c>
       <c r="E61" s="3">
         <v>700</v>
@@ -2308,7 +2308,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="E62" s="3">
         <v>2100</v>
@@ -2317,10 +2317,10 @@
         <v>2300</v>
       </c>
       <c r="G62" s="3">
-        <v>23600</v>
+        <v>23200</v>
       </c>
       <c r="H62" s="3">
-        <v>28300</v>
+        <v>27900</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -2440,19 +2440,19 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>52000</v>
+        <v>51300</v>
       </c>
       <c r="E66" s="3">
-        <v>25700</v>
+        <v>25300</v>
       </c>
       <c r="F66" s="3">
-        <v>48100</v>
+        <v>47400</v>
       </c>
       <c r="G66" s="3">
-        <v>55600</v>
+        <v>54900</v>
       </c>
       <c r="H66" s="3">
-        <v>43800</v>
+        <v>43200</v>
       </c>
       <c r="I66" s="3">
         <v>1900</v>
@@ -2620,25 +2620,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-107700</v>
+        <v>-106300</v>
       </c>
       <c r="E72" s="3">
-        <v>-102500</v>
+        <v>-101200</v>
       </c>
       <c r="F72" s="3">
-        <v>-88300</v>
+        <v>-87200</v>
       </c>
       <c r="G72" s="3">
-        <v>-66300</v>
+        <v>-65400</v>
       </c>
       <c r="H72" s="3">
-        <v>-38500</v>
+        <v>-38000</v>
       </c>
       <c r="I72" s="3">
-        <v>-25900</v>
+        <v>-25500</v>
       </c>
       <c r="J72" s="3">
-        <v>-34700</v>
+        <v>-34300</v>
       </c>
       <c r="K72" s="3">
         <v>-31100</v>
@@ -2752,22 +2752,22 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>103800</v>
+        <v>102400</v>
       </c>
       <c r="E76" s="3">
-        <v>98800</v>
+        <v>97500</v>
       </c>
       <c r="F76" s="3">
-        <v>59500</v>
+        <v>58700</v>
       </c>
       <c r="G76" s="3">
-        <v>9900</v>
+        <v>9700</v>
       </c>
       <c r="H76" s="3">
-        <v>23700</v>
+        <v>23400</v>
       </c>
       <c r="I76" s="3">
-        <v>13600</v>
+        <v>13400</v>
       </c>
       <c r="J76" s="3">
         <v>4500</v>
@@ -2856,25 +2856,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="E81" s="3">
-        <v>-11200</v>
+        <v>-11100</v>
       </c>
       <c r="F81" s="3">
-        <v>-21700</v>
+        <v>-21400</v>
       </c>
       <c r="G81" s="3">
-        <v>-17800</v>
+        <v>-17600</v>
       </c>
       <c r="H81" s="3">
-        <v>-20700</v>
+        <v>-20400</v>
       </c>
       <c r="I81" s="3">
-        <v>-33400</v>
+        <v>-33000</v>
       </c>
       <c r="J81" s="3">
-        <v>-6000</v>
+        <v>-5900</v>
       </c>
       <c r="K81" s="3">
         <v>-7300</v>
@@ -2904,13 +2904,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12600</v>
+        <v>12400</v>
       </c>
       <c r="E83" s="3">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="F83" s="3">
-        <v>4300</v>
+        <v>4200</v>
       </c>
       <c r="G83" s="3">
         <v>3100</v>
@@ -3102,13 +3102,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="E89" s="3">
         <v>-100</v>
       </c>
       <c r="F89" s="3">
-        <v>9300</v>
+        <v>9200</v>
       </c>
       <c r="G89" s="3">
         <v>-2500</v>
@@ -3117,7 +3117,7 @@
         <v>-600</v>
       </c>
       <c r="I89" s="3">
-        <v>-10100</v>
+        <v>-10000</v>
       </c>
       <c r="J89" s="3">
         <v>-2200</v>
@@ -3249,10 +3249,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-25200</v>
+        <v>-24800</v>
       </c>
       <c r="E94" s="3">
-        <v>-35600</v>
+        <v>-35200</v>
       </c>
       <c r="F94" s="3">
         <v>-4100</v>
@@ -3261,7 +3261,7 @@
         <v>-3400</v>
       </c>
       <c r="H94" s="3">
-        <v>-5500</v>
+        <v>-5400</v>
       </c>
       <c r="I94" s="3">
         <v>3100</v>
@@ -3429,25 +3429,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>10500</v>
+        <v>10300</v>
       </c>
       <c r="E100" s="3">
-        <v>18500</v>
+        <v>18300</v>
       </c>
       <c r="F100" s="3">
-        <v>33200</v>
+        <v>32800</v>
       </c>
       <c r="G100" s="3">
         <v>-800</v>
       </c>
       <c r="H100" s="3">
-        <v>12400</v>
+        <v>12200</v>
       </c>
       <c r="I100" s="3">
-        <v>10600</v>
+        <v>10400</v>
       </c>
       <c r="J100" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="K100" s="3">
         <v>6800</v>
@@ -3495,25 +3495,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-7000</v>
+        <v>-6900</v>
       </c>
       <c r="E102" s="3">
-        <v>-15100</v>
+        <v>-14900</v>
       </c>
       <c r="F102" s="3">
-        <v>37900</v>
+        <v>37400</v>
       </c>
       <c r="G102" s="3">
-        <v>-7200</v>
+        <v>-7100</v>
       </c>
       <c r="H102" s="3">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="I102" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="J102" s="3">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="K102" s="3">
         <v>800</v>

--- a/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>BRAG</t>
   </si>
@@ -656,118 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42766</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42400</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42035</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>124800</v>
+        <v>138700</v>
       </c>
       <c r="E8" s="3">
-        <v>85900</v>
+        <v>125700</v>
       </c>
       <c r="F8" s="3">
-        <v>68400</v>
+        <v>86500</v>
       </c>
       <c r="G8" s="3">
-        <v>39200</v>
+        <v>68800</v>
       </c>
       <c r="H8" s="3">
+        <v>39400</v>
+      </c>
+      <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="I8" s="3">
-        <v>15800</v>
-      </c>
       <c r="J8" s="3">
+        <v>15900</v>
+      </c>
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2700</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>58400</v>
+        <v>64600</v>
       </c>
       <c r="E9" s="3">
-        <v>44200</v>
+        <v>58800</v>
       </c>
       <c r="F9" s="3">
-        <v>38600</v>
+        <v>44500</v>
       </c>
       <c r="G9" s="3">
-        <v>21400</v>
+        <v>38900</v>
       </c>
       <c r="H9" s="3">
+        <v>21600</v>
+      </c>
+      <c r="I9" s="3">
         <v>600</v>
       </c>
-      <c r="I9" s="3">
-        <v>8400</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="J9" s="3">
+        <v>8500</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -775,32 +781,35 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>66400</v>
+        <v>74100</v>
       </c>
       <c r="E10" s="3">
-        <v>41700</v>
+        <v>66900</v>
       </c>
       <c r="F10" s="3">
-        <v>29700</v>
+        <v>42000</v>
       </c>
       <c r="G10" s="3">
-        <v>17700</v>
+        <v>29900</v>
       </c>
       <c r="H10" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I10" s="3">
         <v>500</v>
       </c>
-      <c r="I10" s="3">
-        <v>7300</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="J10" s="3">
+        <v>7400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -808,9 +817,12 @@
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +836,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -847,18 +860,21 @@
       <c r="I12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3">
         <v>900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1700</v>
       </c>
       <c r="L12" s="3">
         <v>1700</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,75 +905,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
-        <v>16900</v>
-      </c>
       <c r="G14" s="3">
+        <v>17000</v>
+      </c>
+      <c r="H14" s="3">
         <v>7900</v>
       </c>
-      <c r="H14" s="3">
-        <v>16200</v>
-      </c>
       <c r="I14" s="3">
-        <v>18700</v>
+        <v>16300</v>
       </c>
       <c r="J14" s="3">
+        <v>18800</v>
+      </c>
+      <c r="K14" s="3">
         <v>1800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1600</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12400</v>
+        <v>19400</v>
       </c>
       <c r="E15" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F15" s="3">
         <v>7100</v>
       </c>
-      <c r="F15" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3">
-        <v>800</v>
+      <c r="G15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I15" s="3">
         <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
       </c>
       <c r="L15" s="3">
+        <v>600</v>
+      </c>
+      <c r="M15" s="3">
         <v>500</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,41 +993,45 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>126000</v>
+        <v>139800</v>
       </c>
       <c r="E17" s="3">
-        <v>95400</v>
+        <v>126900</v>
       </c>
       <c r="F17" s="3">
-        <v>85900</v>
+        <v>96100</v>
       </c>
       <c r="G17" s="3">
-        <v>51100</v>
+        <v>86500</v>
       </c>
       <c r="H17" s="3">
-        <v>8100</v>
+        <v>51400</v>
       </c>
       <c r="I17" s="3">
-        <v>48500</v>
+        <v>8200</v>
       </c>
       <c r="J17" s="3">
+        <v>48800</v>
+      </c>
+      <c r="K17" s="3">
         <v>7400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8500</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1010,32 +1039,35 @@
         <v>-1200</v>
       </c>
       <c r="E18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-9600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-17500</v>
-      </c>
       <c r="G18" s="3">
-        <v>-11900</v>
+        <v>-17600</v>
       </c>
       <c r="H18" s="3">
-        <v>-7000</v>
+        <v>-12000</v>
       </c>
       <c r="I18" s="3">
-        <v>-32700</v>
+        <v>-7100</v>
       </c>
       <c r="J18" s="3">
+        <v>-32900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-5800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5800</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,26 +1081,27 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2500</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1076,131 +1109,143 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E21" s="3">
         <v>11100</v>
       </c>
-      <c r="E21" s="3">
-        <v>-2400</v>
-      </c>
       <c r="F21" s="3">
-        <v>-14800</v>
+        <v>-2500</v>
       </c>
       <c r="G21" s="3">
-        <v>-11400</v>
+        <v>-14900</v>
       </c>
       <c r="H21" s="3">
-        <v>-6200</v>
+        <v>-11500</v>
       </c>
       <c r="I21" s="3">
-        <v>-31900</v>
+        <v>-6300</v>
       </c>
       <c r="J21" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-5300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5400</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2800</v>
+        <v>-4300</v>
       </c>
       <c r="E23" s="3">
-        <v>-9800</v>
+        <v>-2900</v>
       </c>
       <c r="F23" s="3">
-        <v>-19600</v>
+        <v>-9900</v>
       </c>
       <c r="G23" s="3">
-        <v>-14500</v>
+        <v>-19700</v>
       </c>
       <c r="H23" s="3">
-        <v>-7000</v>
+        <v>-14600</v>
       </c>
       <c r="I23" s="3">
-        <v>-33100</v>
+        <v>-7100</v>
       </c>
       <c r="J23" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5900</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1213,9 +1258,12 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,75 +1294,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5100</v>
+        <v>-5700</v>
       </c>
       <c r="E26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-11100</v>
       </c>
-      <c r="F26" s="3">
-        <v>-21300</v>
-      </c>
       <c r="G26" s="3">
-        <v>-15300</v>
+        <v>-21500</v>
       </c>
       <c r="H26" s="3">
-        <v>-7000</v>
+        <v>-15400</v>
       </c>
       <c r="I26" s="3">
-        <v>-33100</v>
+        <v>-7100</v>
       </c>
       <c r="J26" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5900</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5100</v>
+        <v>-5700</v>
       </c>
       <c r="E27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-11100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-21300</v>
-      </c>
       <c r="G27" s="3">
-        <v>-15300</v>
+        <v>-21500</v>
       </c>
       <c r="H27" s="3">
-        <v>-7000</v>
+        <v>-15400</v>
       </c>
       <c r="I27" s="3">
-        <v>-33100</v>
+        <v>-7100</v>
       </c>
       <c r="J27" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,42 +1402,48 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-2300</v>
       </c>
-      <c r="H29" s="3">
-        <v>-13400</v>
-      </c>
       <c r="I29" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="J29" s="3">
         <v>100</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,27 +1510,30 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2500</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -1472,47 +1541,53 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5100</v>
+        <v>-5700</v>
       </c>
       <c r="E33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-11100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-21400</v>
-      </c>
       <c r="G33" s="3">
-        <v>-17600</v>
+        <v>-21600</v>
       </c>
       <c r="H33" s="3">
-        <v>-20400</v>
+        <v>-17700</v>
       </c>
       <c r="I33" s="3">
-        <v>-33000</v>
+        <v>-20500</v>
       </c>
       <c r="J33" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,80 +1618,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5100</v>
+        <v>-5700</v>
       </c>
       <c r="E35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-11100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-21400</v>
-      </c>
       <c r="G35" s="3">
-        <v>-17600</v>
+        <v>-21600</v>
       </c>
       <c r="H35" s="3">
-        <v>-20400</v>
+        <v>-17700</v>
       </c>
       <c r="I35" s="3">
-        <v>-33000</v>
+        <v>-20500</v>
       </c>
       <c r="J35" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42766</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42400</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42035</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,41 +1730,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16600</v>
+        <v>13000</v>
       </c>
       <c r="E41" s="3">
-        <v>23600</v>
+        <v>16700</v>
       </c>
       <c r="F41" s="3">
-        <v>38400</v>
+        <v>23700</v>
       </c>
       <c r="G41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="H41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
-        <v>20700</v>
-      </c>
       <c r="I41" s="3">
+        <v>20800</v>
+      </c>
+      <c r="J41" s="3">
         <v>7100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>500</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1710,42 +1799,48 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>24500</v>
+        <v>27600</v>
       </c>
       <c r="E43" s="3">
-        <v>12500</v>
+        <v>24700</v>
       </c>
       <c r="F43" s="3">
-        <v>15400</v>
+        <v>12600</v>
       </c>
       <c r="G43" s="3">
-        <v>9100</v>
+        <v>15500</v>
       </c>
       <c r="H43" s="3">
-        <v>15500</v>
+        <v>9200</v>
       </c>
       <c r="I43" s="3">
+        <v>15600</v>
+      </c>
+      <c r="J43" s="3">
         <v>4900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1776,90 +1871,99 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E45" s="3">
         <v>2700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>900</v>
       </c>
       <c r="I45" s="3">
         <v>1000</v>
       </c>
       <c r="J45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>43800</v>
+        <v>43100</v>
       </c>
       <c r="E46" s="3">
-        <v>39700</v>
+        <v>44100</v>
       </c>
       <c r="F46" s="3">
-        <v>54200</v>
+        <v>40000</v>
       </c>
       <c r="G46" s="3">
-        <v>12300</v>
+        <v>54600</v>
       </c>
       <c r="H46" s="3">
-        <v>14400</v>
+        <v>12400</v>
       </c>
       <c r="I46" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J46" s="3">
         <v>4900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>5</v>
       </c>
@@ -1875,75 +1979,84 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1400</v>
       </c>
       <c r="G48" s="3">
         <v>1500</v>
       </c>
       <c r="H48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>97300</v>
+        <v>88600</v>
       </c>
       <c r="E49" s="3">
-        <v>76300</v>
+        <v>98000</v>
       </c>
       <c r="F49" s="3">
-        <v>46700</v>
+        <v>76800</v>
       </c>
       <c r="G49" s="3">
-        <v>50800</v>
+        <v>47100</v>
       </c>
       <c r="H49" s="3">
-        <v>51800</v>
+        <v>51200</v>
       </c>
       <c r="I49" s="3">
-        <v>10100</v>
+        <v>52200</v>
       </c>
       <c r="J49" s="3">
+        <v>10200</v>
+      </c>
+      <c r="K49" s="3">
         <v>100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2800</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,32 +2123,35 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10800</v>
+        <v>15800</v>
       </c>
       <c r="E52" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F52" s="3">
         <v>5600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
+      <c r="J52" s="3">
+        <v>200</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
@@ -2040,9 +2159,12 @@
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,42 +2195,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>153700</v>
+        <v>153300</v>
       </c>
       <c r="E54" s="3">
-        <v>122800</v>
+        <v>154800</v>
       </c>
       <c r="F54" s="3">
-        <v>106200</v>
+        <v>123700</v>
       </c>
       <c r="G54" s="3">
-        <v>64600</v>
+        <v>106900</v>
       </c>
       <c r="H54" s="3">
-        <v>66700</v>
+        <v>65100</v>
       </c>
       <c r="I54" s="3">
-        <v>15300</v>
+        <v>67100</v>
       </c>
       <c r="J54" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K54" s="3">
         <v>5500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3700</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,161 +2266,174 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E57" s="3">
         <v>6400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
-        <v>9400</v>
-      </c>
       <c r="G57" s="3">
-        <v>13000</v>
+        <v>9500</v>
       </c>
       <c r="H57" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I57" s="3">
         <v>11800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
-      </c>
-      <c r="E58" s="3">
-        <v>200</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
       </c>
       <c r="G58" s="3">
+        <v>200</v>
+      </c>
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2000</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28800</v>
+        <v>25600</v>
       </c>
       <c r="E59" s="3">
-        <v>20200</v>
+        <v>29000</v>
       </c>
       <c r="F59" s="3">
-        <v>34600</v>
+        <v>20300</v>
       </c>
       <c r="G59" s="3">
-        <v>17300</v>
+        <v>34900</v>
       </c>
       <c r="H59" s="3">
-        <v>7500</v>
+        <v>17400</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>35800</v>
+        <v>41400</v>
       </c>
       <c r="E60" s="3">
-        <v>22600</v>
+        <v>36000</v>
       </c>
       <c r="F60" s="3">
-        <v>44200</v>
+        <v>22700</v>
       </c>
       <c r="G60" s="3">
-        <v>30600</v>
+        <v>44600</v>
       </c>
       <c r="H60" s="3">
-        <v>14900</v>
+        <v>30800</v>
       </c>
       <c r="I60" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10300</v>
+        <v>3800</v>
       </c>
       <c r="E61" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F61" s="3">
         <v>700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2301,32 +2443,35 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5200</v>
+        <v>3900</v>
       </c>
       <c r="E62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2300</v>
       </c>
-      <c r="G62" s="3">
-        <v>23200</v>
-      </c>
       <c r="H62" s="3">
-        <v>27900</v>
+        <v>23400</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
+        <v>28100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
@@ -2334,9 +2479,12 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,42 +2587,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>51300</v>
+        <v>49100</v>
       </c>
       <c r="E66" s="3">
-        <v>25300</v>
+        <v>51700</v>
       </c>
       <c r="F66" s="3">
-        <v>47400</v>
+        <v>25500</v>
       </c>
       <c r="G66" s="3">
-        <v>54900</v>
+        <v>47700</v>
       </c>
       <c r="H66" s="3">
-        <v>43200</v>
+        <v>55300</v>
       </c>
       <c r="I66" s="3">
+        <v>43600</v>
+      </c>
+      <c r="J66" s="3">
         <v>1900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2580,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,42 +2783,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-106300</v>
+        <v>-112800</v>
       </c>
       <c r="E72" s="3">
-        <v>-101200</v>
+        <v>-107100</v>
       </c>
       <c r="F72" s="3">
-        <v>-87200</v>
+        <v>-101900</v>
       </c>
       <c r="G72" s="3">
-        <v>-65400</v>
+        <v>-87800</v>
       </c>
       <c r="H72" s="3">
-        <v>-38000</v>
+        <v>-65900</v>
       </c>
       <c r="I72" s="3">
-        <v>-25500</v>
+        <v>-38300</v>
       </c>
       <c r="J72" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-34300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-31100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25700</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,42 +2927,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>102400</v>
+        <v>104200</v>
       </c>
       <c r="E76" s="3">
-        <v>97500</v>
+        <v>103100</v>
       </c>
       <c r="F76" s="3">
-        <v>58700</v>
+        <v>98200</v>
       </c>
       <c r="G76" s="3">
-        <v>9700</v>
+        <v>59200</v>
       </c>
       <c r="H76" s="3">
-        <v>23400</v>
+        <v>9800</v>
       </c>
       <c r="I76" s="3">
-        <v>13400</v>
+        <v>23600</v>
       </c>
       <c r="J76" s="3">
+        <v>13500</v>
+      </c>
+      <c r="K76" s="3">
         <v>4500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>500</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,80 +2999,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42766</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42400</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42035</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5100</v>
+        <v>-5700</v>
       </c>
       <c r="E81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-11100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-21400</v>
-      </c>
       <c r="G81" s="3">
-        <v>-17600</v>
+        <v>-21600</v>
       </c>
       <c r="H81" s="3">
-        <v>-20400</v>
+        <v>-17700</v>
       </c>
       <c r="I81" s="3">
-        <v>-33000</v>
+        <v>-20500</v>
       </c>
       <c r="J81" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,41 +3095,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12400</v>
+        <v>19400</v>
       </c>
       <c r="E83" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F83" s="3">
         <v>7100</v>
       </c>
-      <c r="F83" s="3">
-        <v>4200</v>
-      </c>
       <c r="G83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H83" s="3">
         <v>3100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>800</v>
       </c>
       <c r="I83" s="3">
         <v>800</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
       </c>
       <c r="L83" s="3">
+        <v>600</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,42 +3308,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E89" s="3">
         <v>8500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
-        <v>9200</v>
-      </c>
       <c r="G89" s="3">
+        <v>9300</v>
+      </c>
+      <c r="H89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
-        <v>-10000</v>
-      </c>
       <c r="J89" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,41 +3363,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,42 +3468,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-24800</v>
+        <v>-14400</v>
       </c>
       <c r="E94" s="3">
-        <v>-35200</v>
+        <v>-25000</v>
       </c>
       <c r="F94" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="G94" s="3">
         <v>-4100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3400</v>
       </c>
-      <c r="H94" s="3">
-        <v>-5400</v>
-      </c>
       <c r="I94" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="J94" s="3">
         <v>3100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,8 +3523,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3323,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,106 +3664,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>10300</v>
+        <v>-6200</v>
       </c>
       <c r="E100" s="3">
-        <v>18300</v>
+        <v>10400</v>
       </c>
       <c r="F100" s="3">
-        <v>32800</v>
+        <v>18400</v>
       </c>
       <c r="G100" s="3">
+        <v>33000</v>
+      </c>
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
-        <v>12200</v>
-      </c>
       <c r="I100" s="3">
-        <v>10400</v>
+        <v>12300</v>
       </c>
       <c r="J100" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K100" s="3">
         <v>6100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6900</v>
+        <v>-3700</v>
       </c>
       <c r="E102" s="3">
-        <v>-14900</v>
+        <v>-7000</v>
       </c>
       <c r="F102" s="3">
-        <v>37400</v>
+        <v>-15000</v>
       </c>
       <c r="G102" s="3">
+        <v>37700</v>
+      </c>
+      <c r="H102" s="3">
         <v>-7100</v>
       </c>
-      <c r="H102" s="3">
-        <v>5300</v>
-      </c>
       <c r="I102" s="3">
-        <v>3800</v>
+        <v>5400</v>
       </c>
       <c r="J102" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K102" s="3">
         <v>3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
@@ -719,25 +719,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>138700</v>
+        <v>140700</v>
       </c>
       <c r="E8" s="3">
-        <v>125700</v>
+        <v>127500</v>
       </c>
       <c r="F8" s="3">
-        <v>86500</v>
+        <v>87800</v>
       </c>
       <c r="G8" s="3">
-        <v>68800</v>
+        <v>69800</v>
       </c>
       <c r="H8" s="3">
-        <v>39400</v>
+        <v>40000</v>
       </c>
       <c r="I8" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="J8" s="3">
-        <v>15900</v>
+        <v>16100</v>
       </c>
       <c r="K8" s="3">
         <v>1600</v>
@@ -755,25 +755,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>64600</v>
+        <v>65600</v>
       </c>
       <c r="E9" s="3">
-        <v>58800</v>
+        <v>59700</v>
       </c>
       <c r="F9" s="3">
-        <v>44500</v>
+        <v>45100</v>
       </c>
       <c r="G9" s="3">
-        <v>38900</v>
+        <v>39500</v>
       </c>
       <c r="H9" s="3">
-        <v>21600</v>
+        <v>21900</v>
       </c>
       <c r="I9" s="3">
         <v>600</v>
       </c>
       <c r="J9" s="3">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -791,25 +791,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>74100</v>
+        <v>75100</v>
       </c>
       <c r="E10" s="3">
-        <v>66900</v>
+        <v>67800</v>
       </c>
       <c r="F10" s="3">
-        <v>42000</v>
+        <v>42600</v>
       </c>
       <c r="G10" s="3">
-        <v>29900</v>
+        <v>30400</v>
       </c>
       <c r="H10" s="3">
-        <v>17800</v>
+        <v>18100</v>
       </c>
       <c r="I10" s="3">
         <v>500</v>
       </c>
       <c r="J10" s="3">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -915,25 +915,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-200</v>
+        <v>-900</v>
       </c>
       <c r="E14" s="3">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="F14" s="3">
         <v>2000</v>
       </c>
       <c r="G14" s="3">
-        <v>17000</v>
+        <v>3300</v>
       </c>
       <c r="H14" s="3">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>16300</v>
+        <v>16600</v>
       </c>
       <c r="J14" s="3">
-        <v>18800</v>
+        <v>19100</v>
       </c>
       <c r="K14" s="3">
         <v>1800</v>
@@ -951,13 +951,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>19400</v>
+        <v>19700</v>
       </c>
       <c r="E15" s="3">
-        <v>12500</v>
+        <v>12700</v>
       </c>
       <c r="F15" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="G15" s="3">
         <v>4300</v>
@@ -969,7 +969,7 @@
         <v>800</v>
       </c>
       <c r="J15" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
@@ -1000,25 +1000,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>139800</v>
+        <v>141900</v>
       </c>
       <c r="E17" s="3">
-        <v>126900</v>
+        <v>128700</v>
       </c>
       <c r="F17" s="3">
-        <v>96100</v>
+        <v>97500</v>
       </c>
       <c r="G17" s="3">
-        <v>86500</v>
+        <v>87700</v>
       </c>
       <c r="H17" s="3">
-        <v>51400</v>
+        <v>52200</v>
       </c>
       <c r="I17" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="J17" s="3">
-        <v>48800</v>
+        <v>49500</v>
       </c>
       <c r="K17" s="3">
         <v>7400</v>
@@ -1042,19 +1042,19 @@
         <v>-1200</v>
       </c>
       <c r="F18" s="3">
-        <v>-9600</v>
+        <v>-9800</v>
       </c>
       <c r="G18" s="3">
-        <v>-17600</v>
+        <v>-17900</v>
       </c>
       <c r="H18" s="3">
-        <v>-12000</v>
+        <v>-12200</v>
       </c>
       <c r="I18" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="J18" s="3">
-        <v>-32900</v>
+        <v>-33400</v>
       </c>
       <c r="K18" s="3">
         <v>-5800</v>
@@ -1097,10 +1097,10 @@
         <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>-1500</v>
+        <v>-1600</v>
       </c>
       <c r="H20" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>18300</v>
+        <v>18600</v>
       </c>
       <c r="E21" s="3">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="F21" s="3">
         <v>-2500</v>
       </c>
       <c r="G21" s="3">
-        <v>-14900</v>
+        <v>-15100</v>
       </c>
       <c r="H21" s="3">
-        <v>-11500</v>
+        <v>-11600</v>
       </c>
       <c r="I21" s="3">
         <v>-6300</v>
       </c>
       <c r="J21" s="3">
-        <v>-32100</v>
+        <v>-32600</v>
       </c>
       <c r="K21" s="3">
         <v>-5300</v>
@@ -1196,25 +1196,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="E23" s="3">
         <v>-2900</v>
       </c>
       <c r="F23" s="3">
-        <v>-9900</v>
+        <v>-10100</v>
       </c>
       <c r="G23" s="3">
-        <v>-19700</v>
+        <v>-20000</v>
       </c>
       <c r="H23" s="3">
-        <v>-14600</v>
+        <v>-14800</v>
       </c>
       <c r="I23" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="J23" s="3">
-        <v>-33300</v>
+        <v>-33800</v>
       </c>
       <c r="K23" s="3">
         <v>-5900</v>
@@ -1232,7 +1232,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="E24" s="3">
         <v>2300</v>
@@ -1304,25 +1304,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="E26" s="3">
         <v>-5200</v>
       </c>
       <c r="F26" s="3">
-        <v>-11100</v>
+        <v>-11300</v>
       </c>
       <c r="G26" s="3">
-        <v>-21500</v>
+        <v>-21800</v>
       </c>
       <c r="H26" s="3">
-        <v>-15400</v>
+        <v>-15600</v>
       </c>
       <c r="I26" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="J26" s="3">
-        <v>-33300</v>
+        <v>-33800</v>
       </c>
       <c r="K26" s="3">
         <v>-5900</v>
@@ -1340,25 +1340,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="E27" s="3">
         <v>-5200</v>
       </c>
       <c r="F27" s="3">
-        <v>-11100</v>
+        <v>-11300</v>
       </c>
       <c r="G27" s="3">
-        <v>-21500</v>
+        <v>-21800</v>
       </c>
       <c r="H27" s="3">
-        <v>-15400</v>
+        <v>-15600</v>
       </c>
       <c r="I27" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="J27" s="3">
-        <v>-33300</v>
+        <v>-33800</v>
       </c>
       <c r="K27" s="3">
         <v>-5900</v>
@@ -1424,10 +1424,10 @@
         <v>-100</v>
       </c>
       <c r="H29" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="I29" s="3">
-        <v>-13500</v>
+        <v>-13700</v>
       </c>
       <c r="J29" s="3">
         <v>100</v>
@@ -1529,10 +1529,10 @@
         <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="H32" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -1556,25 +1556,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="E33" s="3">
         <v>-5200</v>
       </c>
       <c r="F33" s="3">
-        <v>-11100</v>
+        <v>-11300</v>
       </c>
       <c r="G33" s="3">
-        <v>-21600</v>
+        <v>-21900</v>
       </c>
       <c r="H33" s="3">
-        <v>-17700</v>
+        <v>-18000</v>
       </c>
       <c r="I33" s="3">
-        <v>-20500</v>
+        <v>-20800</v>
       </c>
       <c r="J33" s="3">
-        <v>-33200</v>
+        <v>-33700</v>
       </c>
       <c r="K33" s="3">
         <v>-5900</v>
@@ -1628,25 +1628,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="E35" s="3">
         <v>-5200</v>
       </c>
       <c r="F35" s="3">
-        <v>-11100</v>
+        <v>-11300</v>
       </c>
       <c r="G35" s="3">
-        <v>-21600</v>
+        <v>-21900</v>
       </c>
       <c r="H35" s="3">
-        <v>-17700</v>
+        <v>-18000</v>
       </c>
       <c r="I35" s="3">
-        <v>-20500</v>
+        <v>-20800</v>
       </c>
       <c r="J35" s="3">
-        <v>-33200</v>
+        <v>-33700</v>
       </c>
       <c r="K35" s="3">
         <v>-5900</v>
@@ -1737,25 +1737,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13000</v>
+        <v>13200</v>
       </c>
       <c r="E41" s="3">
-        <v>16700</v>
+        <v>17000</v>
       </c>
       <c r="F41" s="3">
-        <v>23700</v>
+        <v>24100</v>
       </c>
       <c r="G41" s="3">
-        <v>38700</v>
+        <v>39300</v>
       </c>
       <c r="H41" s="3">
         <v>1000</v>
       </c>
       <c r="I41" s="3">
-        <v>20800</v>
+        <v>21100</v>
       </c>
       <c r="J41" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="K41" s="3">
         <v>5000</v>
@@ -1809,25 +1809,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>27600</v>
+        <v>28000</v>
       </c>
       <c r="E43" s="3">
-        <v>24700</v>
+        <v>25000</v>
       </c>
       <c r="F43" s="3">
-        <v>12600</v>
+        <v>12800</v>
       </c>
       <c r="G43" s="3">
-        <v>15500</v>
+        <v>15700</v>
       </c>
       <c r="H43" s="3">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="I43" s="3">
-        <v>15600</v>
+        <v>15800</v>
       </c>
       <c r="J43" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -1887,7 +1887,7 @@
         <v>2700</v>
       </c>
       <c r="F45" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
@@ -1917,25 +1917,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>43100</v>
+        <v>43800</v>
       </c>
       <c r="E46" s="3">
-        <v>44100</v>
+        <v>44700</v>
       </c>
       <c r="F46" s="3">
-        <v>40000</v>
+        <v>40600</v>
       </c>
       <c r="G46" s="3">
-        <v>54600</v>
+        <v>55400</v>
       </c>
       <c r="H46" s="3">
-        <v>12400</v>
+        <v>12500</v>
       </c>
       <c r="I46" s="3">
-        <v>14500</v>
+        <v>14700</v>
       </c>
       <c r="J46" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="K46" s="3">
         <v>5400</v>
@@ -1989,13 +1989,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="E48" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="F48" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G48" s="3">
         <v>1500</v>
@@ -2025,25 +2025,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>88600</v>
+        <v>89900</v>
       </c>
       <c r="E49" s="3">
-        <v>98000</v>
+        <v>99400</v>
       </c>
       <c r="F49" s="3">
-        <v>76800</v>
+        <v>77900</v>
       </c>
       <c r="G49" s="3">
-        <v>47100</v>
+        <v>47800</v>
       </c>
       <c r="H49" s="3">
-        <v>51200</v>
+        <v>51900</v>
       </c>
       <c r="I49" s="3">
-        <v>52200</v>
+        <v>53000</v>
       </c>
       <c r="J49" s="3">
-        <v>10200</v>
+        <v>10400</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -2133,16 +2133,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15800</v>
+        <v>16100</v>
       </c>
       <c r="E52" s="3">
-        <v>10900</v>
+        <v>11100</v>
       </c>
       <c r="F52" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="G52" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -2205,25 +2205,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>153300</v>
+        <v>155500</v>
       </c>
       <c r="E54" s="3">
-        <v>154800</v>
+        <v>157100</v>
       </c>
       <c r="F54" s="3">
-        <v>123700</v>
+        <v>125500</v>
       </c>
       <c r="G54" s="3">
-        <v>106900</v>
+        <v>108500</v>
       </c>
       <c r="H54" s="3">
-        <v>65100</v>
+        <v>66000</v>
       </c>
       <c r="I54" s="3">
-        <v>67100</v>
+        <v>68100</v>
       </c>
       <c r="J54" s="3">
-        <v>15400</v>
+        <v>15700</v>
       </c>
       <c r="K54" s="3">
         <v>5500</v>
@@ -2273,25 +2273,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="E57" s="3">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="F57" s="3">
         <v>2200</v>
       </c>
       <c r="G57" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="H57" s="3">
-        <v>13100</v>
+        <v>13300</v>
       </c>
       <c r="I57" s="3">
-        <v>11800</v>
+        <v>12000</v>
       </c>
       <c r="J57" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="K57" s="3">
         <v>400</v>
@@ -2345,22 +2345,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25600</v>
+        <v>25900</v>
       </c>
       <c r="E59" s="3">
-        <v>29000</v>
+        <v>29500</v>
       </c>
       <c r="F59" s="3">
-        <v>20300</v>
+        <v>20600</v>
       </c>
       <c r="G59" s="3">
-        <v>34900</v>
+        <v>35400</v>
       </c>
       <c r="H59" s="3">
-        <v>17400</v>
+        <v>17700</v>
       </c>
       <c r="I59" s="3">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
@@ -2381,25 +2381,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>41400</v>
+        <v>42000</v>
       </c>
       <c r="E60" s="3">
-        <v>36000</v>
+        <v>36600</v>
       </c>
       <c r="F60" s="3">
-        <v>22700</v>
+        <v>23000</v>
       </c>
       <c r="G60" s="3">
-        <v>44600</v>
+        <v>45200</v>
       </c>
       <c r="H60" s="3">
-        <v>30800</v>
+        <v>31300</v>
       </c>
       <c r="I60" s="3">
-        <v>15000</v>
+        <v>15200</v>
       </c>
       <c r="J60" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="K60" s="3">
         <v>1100</v>
@@ -2417,10 +2417,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="E61" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="F61" s="3">
         <v>700</v>
@@ -2453,7 +2453,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="E62" s="3">
         <v>5300</v>
@@ -2462,13 +2462,13 @@
         <v>2100</v>
       </c>
       <c r="G62" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="H62" s="3">
-        <v>23400</v>
+        <v>23800</v>
       </c>
       <c r="I62" s="3">
-        <v>28100</v>
+        <v>28500</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -2597,25 +2597,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>49100</v>
+        <v>49800</v>
       </c>
       <c r="E66" s="3">
-        <v>51700</v>
+        <v>52400</v>
       </c>
       <c r="F66" s="3">
-        <v>25500</v>
+        <v>25900</v>
       </c>
       <c r="G66" s="3">
-        <v>47700</v>
+        <v>48400</v>
       </c>
       <c r="H66" s="3">
-        <v>55300</v>
+        <v>56100</v>
       </c>
       <c r="I66" s="3">
-        <v>43600</v>
+        <v>44200</v>
       </c>
       <c r="J66" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="K66" s="3">
         <v>1100</v>
@@ -2793,25 +2793,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-112800</v>
+        <v>-114500</v>
       </c>
       <c r="E72" s="3">
-        <v>-107100</v>
+        <v>-108600</v>
       </c>
       <c r="F72" s="3">
-        <v>-101900</v>
+        <v>-103400</v>
       </c>
       <c r="G72" s="3">
-        <v>-87800</v>
+        <v>-89100</v>
       </c>
       <c r="H72" s="3">
-        <v>-65900</v>
+        <v>-66900</v>
       </c>
       <c r="I72" s="3">
-        <v>-38300</v>
+        <v>-38800</v>
       </c>
       <c r="J72" s="3">
-        <v>-25700</v>
+        <v>-26100</v>
       </c>
       <c r="K72" s="3">
         <v>-34300</v>
@@ -2937,25 +2937,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>104200</v>
+        <v>105700</v>
       </c>
       <c r="E76" s="3">
-        <v>103100</v>
+        <v>104600</v>
       </c>
       <c r="F76" s="3">
-        <v>98200</v>
+        <v>99600</v>
       </c>
       <c r="G76" s="3">
-        <v>59200</v>
+        <v>60000</v>
       </c>
       <c r="H76" s="3">
-        <v>9800</v>
+        <v>10000</v>
       </c>
       <c r="I76" s="3">
-        <v>23600</v>
+        <v>23900</v>
       </c>
       <c r="J76" s="3">
-        <v>13500</v>
+        <v>13700</v>
       </c>
       <c r="K76" s="3">
         <v>4500</v>
@@ -3050,25 +3050,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="E81" s="3">
         <v>-5200</v>
       </c>
       <c r="F81" s="3">
-        <v>-11100</v>
+        <v>-11300</v>
       </c>
       <c r="G81" s="3">
-        <v>-21600</v>
+        <v>-21900</v>
       </c>
       <c r="H81" s="3">
-        <v>-17700</v>
+        <v>-18000</v>
       </c>
       <c r="I81" s="3">
-        <v>-20500</v>
+        <v>-20800</v>
       </c>
       <c r="J81" s="3">
-        <v>-33200</v>
+        <v>-33700</v>
       </c>
       <c r="K81" s="3">
         <v>-5900</v>
@@ -3102,13 +3102,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>19400</v>
+        <v>19700</v>
       </c>
       <c r="E83" s="3">
-        <v>12500</v>
+        <v>12700</v>
       </c>
       <c r="F83" s="3">
-        <v>7100</v>
+        <v>7200</v>
       </c>
       <c r="G83" s="3">
         <v>4300</v>
@@ -3120,7 +3120,7 @@
         <v>800</v>
       </c>
       <c r="J83" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
@@ -3318,25 +3318,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>17400</v>
+        <v>17700</v>
       </c>
       <c r="E89" s="3">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="F89" s="3">
         <v>-100</v>
       </c>
       <c r="G89" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="H89" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="I89" s="3">
         <v>-600</v>
       </c>
       <c r="J89" s="3">
-        <v>-10100</v>
+        <v>-10200</v>
       </c>
       <c r="K89" s="3">
         <v>-2200</v>
@@ -3478,22 +3478,22 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-14400</v>
+        <v>-14600</v>
       </c>
       <c r="E94" s="3">
-        <v>-25000</v>
+        <v>-25400</v>
       </c>
       <c r="F94" s="3">
-        <v>-35400</v>
+        <v>-35900</v>
       </c>
       <c r="G94" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="H94" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="I94" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="J94" s="3">
         <v>3100</v>
@@ -3674,25 +3674,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-6200</v>
+        <v>-6300</v>
       </c>
       <c r="E100" s="3">
-        <v>10400</v>
+        <v>10500</v>
       </c>
       <c r="F100" s="3">
-        <v>18400</v>
+        <v>18700</v>
       </c>
       <c r="G100" s="3">
-        <v>33000</v>
+        <v>33500</v>
       </c>
       <c r="H100" s="3">
         <v>-800</v>
       </c>
       <c r="I100" s="3">
-        <v>12300</v>
+        <v>12500</v>
       </c>
       <c r="J100" s="3">
-        <v>10500</v>
+        <v>10600</v>
       </c>
       <c r="K100" s="3">
         <v>6100</v>
@@ -3749,16 +3749,16 @@
         <v>-3700</v>
       </c>
       <c r="E102" s="3">
-        <v>-7000</v>
+        <v>-7100</v>
       </c>
       <c r="F102" s="3">
-        <v>-15000</v>
+        <v>-15200</v>
       </c>
       <c r="G102" s="3">
-        <v>37700</v>
+        <v>38200</v>
       </c>
       <c r="H102" s="3">
-        <v>-7100</v>
+        <v>-7200</v>
       </c>
       <c r="I102" s="3">
         <v>5400</v>

--- a/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>BRAG</t>
   </si>
@@ -719,25 +719,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>140700</v>
+        <v>103400</v>
       </c>
       <c r="E8" s="3">
-        <v>127500</v>
+        <v>90600</v>
       </c>
       <c r="F8" s="3">
-        <v>87800</v>
+        <v>66300</v>
       </c>
       <c r="G8" s="3">
-        <v>69800</v>
+        <v>56800</v>
       </c>
       <c r="H8" s="3">
-        <v>40000</v>
+        <v>29800</v>
       </c>
       <c r="I8" s="3">
-        <v>1200</v>
+        <v>3400</v>
       </c>
       <c r="J8" s="3">
-        <v>16100</v>
+        <v>8300</v>
       </c>
       <c r="K8" s="3">
         <v>1600</v>
@@ -755,25 +755,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>65600</v>
+        <v>48200</v>
       </c>
       <c r="E9" s="3">
-        <v>59700</v>
+        <v>42400</v>
       </c>
       <c r="F9" s="3">
-        <v>45100</v>
+        <v>34100</v>
       </c>
       <c r="G9" s="3">
-        <v>39500</v>
+        <v>32100</v>
       </c>
       <c r="H9" s="3">
-        <v>21900</v>
+        <v>16300</v>
       </c>
       <c r="I9" s="3">
-        <v>600</v>
+        <v>1600</v>
       </c>
       <c r="J9" s="3">
-        <v>8600</v>
+        <v>4400</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -791,25 +791,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>75100</v>
+        <v>55200</v>
       </c>
       <c r="E10" s="3">
-        <v>67800</v>
+        <v>48200</v>
       </c>
       <c r="F10" s="3">
-        <v>42600</v>
+        <v>32200</v>
       </c>
       <c r="G10" s="3">
-        <v>30400</v>
+        <v>24700</v>
       </c>
       <c r="H10" s="3">
-        <v>18100</v>
+        <v>13500</v>
       </c>
       <c r="I10" s="3">
-        <v>500</v>
+        <v>1700</v>
       </c>
       <c r="J10" s="3">
-        <v>7500</v>
+        <v>3900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -842,26 +842,26 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>5</v>
+      <c r="D12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>900</v>
+      </c>
+      <c r="H12" s="3">
+        <v>100</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
+      <c r="J12" s="3">
+        <v>0</v>
       </c>
       <c r="K12" s="3">
         <v>900</v>
@@ -915,25 +915,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-900</v>
+        <v>300</v>
       </c>
       <c r="E14" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="F14" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="G14" s="3">
-        <v>3300</v>
+        <v>15300</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="I14" s="3">
-        <v>16600</v>
+        <v>2500</v>
       </c>
       <c r="J14" s="3">
-        <v>19100</v>
+        <v>10000</v>
       </c>
       <c r="K14" s="3">
         <v>1800</v>
@@ -951,25 +951,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>19700</v>
+        <v>14400</v>
       </c>
       <c r="E15" s="3">
-        <v>12700</v>
+        <v>9000</v>
       </c>
       <c r="F15" s="3">
-        <v>7200</v>
+        <v>5500</v>
       </c>
       <c r="G15" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
+        <v>3500</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2300</v>
       </c>
       <c r="I15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
@@ -1000,25 +1000,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>141900</v>
+        <v>104300</v>
       </c>
       <c r="E17" s="3">
-        <v>128700</v>
+        <v>91400</v>
       </c>
       <c r="F17" s="3">
-        <v>97500</v>
+        <v>72000</v>
       </c>
       <c r="G17" s="3">
-        <v>87700</v>
+        <v>57300</v>
       </c>
       <c r="H17" s="3">
-        <v>52200</v>
+        <v>32700</v>
       </c>
       <c r="I17" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="J17" s="3">
-        <v>49500</v>
+        <v>15500</v>
       </c>
       <c r="K17" s="3">
         <v>7400</v>
@@ -1036,25 +1036,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1200</v>
+        <v>-1000</v>
       </c>
       <c r="E18" s="3">
-        <v>-1200</v>
+        <v>-800</v>
       </c>
       <c r="F18" s="3">
-        <v>-9800</v>
+        <v>-5700</v>
       </c>
       <c r="G18" s="3">
-        <v>-17900</v>
+        <v>-500</v>
       </c>
       <c r="H18" s="3">
-        <v>-12200</v>
+        <v>-2900</v>
       </c>
       <c r="I18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-7200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-33400</v>
       </c>
       <c r="K18" s="3">
         <v>-5800</v>
@@ -1088,19 +1088,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>-200</v>
-      </c>
       <c r="F20" s="3">
-        <v>100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1600</v>
+        <v>200</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="3">
-        <v>-2600</v>
+        <v>1900</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>18600</v>
+        <v>13500</v>
       </c>
       <c r="E21" s="3">
-        <v>11300</v>
+        <v>8100</v>
       </c>
       <c r="F21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H21" s="3">
         <v>-2500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-15100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-11600</v>
-      </c>
       <c r="I21" s="3">
-        <v>-6300</v>
+        <v>-2900</v>
       </c>
       <c r="J21" s="3">
-        <v>-32600</v>
+        <v>-6800</v>
       </c>
       <c r="K21" s="3">
         <v>-5300</v>
@@ -1160,25 +1160,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3300</v>
+        <v>2000</v>
       </c>
       <c r="E22" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="F22" s="3">
+        <v>300</v>
+      </c>
+      <c r="G22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3">
-        <v>500</v>
-      </c>
       <c r="H22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1196,25 +1196,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-4400</v>
+        <v>-3200</v>
       </c>
       <c r="E23" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="F23" s="3">
-        <v>-10100</v>
+        <v>-7600</v>
       </c>
       <c r="G23" s="3">
-        <v>-20000</v>
+        <v>-16200</v>
       </c>
       <c r="H23" s="3">
-        <v>-14800</v>
+        <v>-11000</v>
       </c>
       <c r="I23" s="3">
-        <v>-7200</v>
+        <v>-5500</v>
       </c>
       <c r="J23" s="3">
-        <v>-33800</v>
+        <v>-17400</v>
       </c>
       <c r="K23" s="3">
         <v>-5900</v>
@@ -1232,25 +1232,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="E24" s="3">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="F24" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G24" s="3">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="H24" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1304,25 +1304,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5800</v>
+        <v>-4200</v>
       </c>
       <c r="E26" s="3">
-        <v>-5200</v>
+        <v>-3700</v>
       </c>
       <c r="F26" s="3">
-        <v>-11300</v>
+        <v>-8500</v>
       </c>
       <c r="G26" s="3">
-        <v>-21800</v>
+        <v>-17700</v>
       </c>
       <c r="H26" s="3">
-        <v>-15600</v>
+        <v>-11600</v>
       </c>
       <c r="I26" s="3">
-        <v>-7200</v>
+        <v>-5500</v>
       </c>
       <c r="J26" s="3">
-        <v>-33800</v>
+        <v>-17400</v>
       </c>
       <c r="K26" s="3">
         <v>-5900</v>
@@ -1340,25 +1340,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5800</v>
+        <v>-4200</v>
       </c>
       <c r="E27" s="3">
-        <v>-5200</v>
+        <v>-3700</v>
       </c>
       <c r="F27" s="3">
-        <v>-11300</v>
+        <v>-8500</v>
       </c>
       <c r="G27" s="3">
-        <v>-21800</v>
+        <v>-17800</v>
       </c>
       <c r="H27" s="3">
-        <v>-15600</v>
+        <v>-13400</v>
       </c>
       <c r="I27" s="3">
-        <v>-7200</v>
+        <v>-15900</v>
       </c>
       <c r="J27" s="3">
-        <v>-33800</v>
+        <v>-17400</v>
       </c>
       <c r="K27" s="3">
         <v>-5900</v>
@@ -1411,11 +1411,11 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1424,13 +1424,13 @@
         <v>-100</v>
       </c>
       <c r="H29" s="3">
-        <v>-2400</v>
+        <v>-1800</v>
       </c>
       <c r="I29" s="3">
-        <v>-13700</v>
+        <v>-10400</v>
       </c>
       <c r="J29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1520,19 +1520,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>200</v>
-      </c>
       <c r="F32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1600</v>
+        <v>-200</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H32" s="3">
-        <v>2600</v>
+        <v>-1900</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -1556,25 +1556,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5800</v>
+        <v>-4200</v>
       </c>
       <c r="E33" s="3">
-        <v>-5200</v>
+        <v>-3700</v>
       </c>
       <c r="F33" s="3">
-        <v>-11300</v>
+        <v>-8500</v>
       </c>
       <c r="G33" s="3">
-        <v>-21900</v>
+        <v>-17800</v>
       </c>
       <c r="H33" s="3">
-        <v>-18000</v>
+        <v>-13400</v>
       </c>
       <c r="I33" s="3">
-        <v>-20800</v>
+        <v>-15900</v>
       </c>
       <c r="J33" s="3">
-        <v>-33700</v>
+        <v>-17400</v>
       </c>
       <c r="K33" s="3">
         <v>-5900</v>
@@ -1628,25 +1628,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5800</v>
+        <v>-4200</v>
       </c>
       <c r="E35" s="3">
-        <v>-5200</v>
+        <v>-3700</v>
       </c>
       <c r="F35" s="3">
-        <v>-11300</v>
+        <v>-8500</v>
       </c>
       <c r="G35" s="3">
-        <v>-21900</v>
+        <v>-17800</v>
       </c>
       <c r="H35" s="3">
-        <v>-18000</v>
+        <v>-13400</v>
       </c>
       <c r="I35" s="3">
-        <v>-20800</v>
+        <v>-15900</v>
       </c>
       <c r="J35" s="3">
-        <v>-33700</v>
+        <v>-17400</v>
       </c>
       <c r="K35" s="3">
         <v>-5900</v>
@@ -1737,25 +1737,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13200</v>
+        <v>9700</v>
       </c>
       <c r="E41" s="3">
-        <v>17000</v>
+        <v>12100</v>
       </c>
       <c r="F41" s="3">
-        <v>24100</v>
+        <v>18200</v>
       </c>
       <c r="G41" s="3">
-        <v>39300</v>
+        <v>31900</v>
       </c>
       <c r="H41" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="I41" s="3">
-        <v>21100</v>
+        <v>6300</v>
       </c>
       <c r="J41" s="3">
-        <v>7200</v>
+        <v>2300</v>
       </c>
       <c r="K41" s="3">
         <v>5000</v>
@@ -1773,13 +1773,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -1809,25 +1809,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>28000</v>
+        <v>20600</v>
       </c>
       <c r="E43" s="3">
-        <v>25000</v>
+        <v>17800</v>
       </c>
       <c r="F43" s="3">
-        <v>12800</v>
+        <v>9600</v>
       </c>
       <c r="G43" s="3">
-        <v>15700</v>
+        <v>12600</v>
       </c>
       <c r="H43" s="3">
-        <v>9300</v>
+        <v>6900</v>
       </c>
       <c r="I43" s="3">
-        <v>15800</v>
+        <v>4700</v>
       </c>
       <c r="J43" s="3">
-        <v>5000</v>
+        <v>1600</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -1844,26 +1844,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1881,25 +1881,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>2700</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>3700</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1000</v>
+        <v>1300</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
@@ -1917,25 +1917,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>43800</v>
+        <v>32200</v>
       </c>
       <c r="E46" s="3">
-        <v>44700</v>
+        <v>31800</v>
       </c>
       <c r="F46" s="3">
-        <v>40600</v>
+        <v>30700</v>
       </c>
       <c r="G46" s="3">
-        <v>55400</v>
+        <v>45000</v>
       </c>
       <c r="H46" s="3">
-        <v>12500</v>
+        <v>9400</v>
       </c>
       <c r="I46" s="3">
-        <v>14700</v>
+        <v>11200</v>
       </c>
       <c r="J46" s="3">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="K46" s="3">
         <v>5400</v>
@@ -1958,11 +1958,11 @@
       <c r="E47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>5</v>
@@ -1989,22 +1989,22 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5800</v>
+        <v>4300</v>
       </c>
       <c r="E48" s="3">
-        <v>1900</v>
+        <v>1300</v>
       </c>
       <c r="F48" s="3">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="G48" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="H48" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="I48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
@@ -2025,25 +2025,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>89900</v>
+        <v>66000</v>
       </c>
       <c r="E49" s="3">
-        <v>99400</v>
+        <v>70600</v>
       </c>
       <c r="F49" s="3">
-        <v>77900</v>
+        <v>58900</v>
       </c>
       <c r="G49" s="3">
-        <v>47800</v>
+        <v>38800</v>
       </c>
       <c r="H49" s="3">
-        <v>51900</v>
+        <v>37400</v>
       </c>
       <c r="I49" s="3">
-        <v>53000</v>
+        <v>40300</v>
       </c>
       <c r="J49" s="3">
-        <v>10400</v>
+        <v>8100</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -2133,25 +2133,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16100</v>
+        <v>400</v>
       </c>
       <c r="E52" s="3">
-        <v>11100</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
-        <v>200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>200</v>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
@@ -2205,25 +2205,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>155500</v>
+        <v>114300</v>
       </c>
       <c r="E54" s="3">
-        <v>157100</v>
+        <v>111600</v>
       </c>
       <c r="F54" s="3">
-        <v>125500</v>
+        <v>94800</v>
       </c>
       <c r="G54" s="3">
-        <v>108500</v>
+        <v>88200</v>
       </c>
       <c r="H54" s="3">
-        <v>66000</v>
+        <v>49200</v>
       </c>
       <c r="I54" s="3">
-        <v>68100</v>
+        <v>51800</v>
       </c>
       <c r="J54" s="3">
-        <v>15700</v>
+        <v>12800</v>
       </c>
       <c r="K54" s="3">
         <v>5500</v>
@@ -2273,25 +2273,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11300</v>
+        <v>8300</v>
       </c>
       <c r="E57" s="3">
-        <v>6500</v>
+        <v>4600</v>
       </c>
       <c r="F57" s="3">
-        <v>2200</v>
+        <v>1700</v>
       </c>
       <c r="G57" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="H57" s="3">
-        <v>13300</v>
+        <v>5800</v>
       </c>
       <c r="I57" s="3">
-        <v>12000</v>
+        <v>6200</v>
       </c>
       <c r="J57" s="3">
-        <v>5100</v>
+        <v>1400</v>
       </c>
       <c r="K57" s="3">
         <v>400</v>
@@ -2309,10 +2309,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4700</v>
+        <v>3500</v>
       </c>
       <c r="E58" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -2321,10 +2321,10 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2345,25 +2345,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25900</v>
+        <v>3600</v>
       </c>
       <c r="E59" s="3">
-        <v>29500</v>
+        <v>5100</v>
       </c>
       <c r="F59" s="3">
-        <v>20600</v>
+        <v>1000</v>
       </c>
       <c r="G59" s="3">
-        <v>35400</v>
+        <v>16000</v>
       </c>
       <c r="H59" s="3">
-        <v>17700</v>
+        <v>13900</v>
       </c>
       <c r="I59" s="3">
-        <v>7700</v>
+        <v>3600</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -2381,25 +2381,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>42000</v>
+        <v>30800</v>
       </c>
       <c r="E60" s="3">
-        <v>36600</v>
+        <v>26000</v>
       </c>
       <c r="F60" s="3">
-        <v>23000</v>
+        <v>17400</v>
       </c>
       <c r="G60" s="3">
-        <v>45200</v>
+        <v>36700</v>
       </c>
       <c r="H60" s="3">
-        <v>31300</v>
+        <v>23300</v>
       </c>
       <c r="I60" s="3">
-        <v>15200</v>
+        <v>11600</v>
       </c>
       <c r="J60" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="K60" s="3">
         <v>1100</v>
@@ -2417,22 +2417,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3900</v>
+        <v>2800</v>
       </c>
       <c r="E61" s="3">
-        <v>10500</v>
+        <v>7500</v>
       </c>
       <c r="F61" s="3">
+        <v>500</v>
+      </c>
+      <c r="G61" s="3">
         <v>700</v>
       </c>
-      <c r="G61" s="3">
-        <v>900</v>
-      </c>
       <c r="H61" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="I61" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2453,25 +2453,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="E62" s="3">
-        <v>5300</v>
+        <v>2500</v>
       </c>
       <c r="F62" s="3">
-        <v>2100</v>
+        <v>200</v>
       </c>
       <c r="G62" s="3">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="H62" s="3">
-        <v>23800</v>
+        <v>16000</v>
       </c>
       <c r="I62" s="3">
-        <v>28500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>19800</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
@@ -2597,25 +2597,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>49800</v>
+        <v>36600</v>
       </c>
       <c r="E66" s="3">
-        <v>52400</v>
+        <v>37200</v>
       </c>
       <c r="F66" s="3">
-        <v>25900</v>
+        <v>19600</v>
       </c>
       <c r="G66" s="3">
-        <v>48400</v>
+        <v>39400</v>
       </c>
       <c r="H66" s="3">
-        <v>56100</v>
+        <v>41800</v>
       </c>
       <c r="I66" s="3">
-        <v>44200</v>
+        <v>33600</v>
       </c>
       <c r="J66" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="K66" s="3">
         <v>1100</v>
@@ -2793,25 +2793,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-114500</v>
+        <v>-84100</v>
       </c>
       <c r="E72" s="3">
-        <v>-108600</v>
+        <v>-77200</v>
       </c>
       <c r="F72" s="3">
-        <v>-103400</v>
+        <v>-78200</v>
       </c>
       <c r="G72" s="3">
-        <v>-89100</v>
+        <v>-74900</v>
       </c>
       <c r="H72" s="3">
-        <v>-66900</v>
+        <v>-52400</v>
       </c>
       <c r="I72" s="3">
-        <v>-38800</v>
+        <v>-39700</v>
       </c>
       <c r="J72" s="3">
-        <v>-26100</v>
+        <v>-25700</v>
       </c>
       <c r="K72" s="3">
         <v>-34300</v>
@@ -2937,25 +2937,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>105700</v>
+        <v>77600</v>
       </c>
       <c r="E76" s="3">
-        <v>104600</v>
+        <v>74300</v>
       </c>
       <c r="F76" s="3">
-        <v>99600</v>
+        <v>75300</v>
       </c>
       <c r="G76" s="3">
-        <v>60000</v>
+        <v>48800</v>
       </c>
       <c r="H76" s="3">
-        <v>10000</v>
+        <v>7400</v>
       </c>
       <c r="I76" s="3">
-        <v>23900</v>
+        <v>18200</v>
       </c>
       <c r="J76" s="3">
-        <v>13700</v>
+        <v>11200</v>
       </c>
       <c r="K76" s="3">
         <v>4500</v>
@@ -3050,25 +3050,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5800</v>
+        <v>-4200</v>
       </c>
       <c r="E81" s="3">
-        <v>-5200</v>
+        <v>-3700</v>
       </c>
       <c r="F81" s="3">
-        <v>-11300</v>
+        <v>-8500</v>
       </c>
       <c r="G81" s="3">
-        <v>-21900</v>
+        <v>-17800</v>
       </c>
       <c r="H81" s="3">
-        <v>-18000</v>
+        <v>-13400</v>
       </c>
       <c r="I81" s="3">
-        <v>-20800</v>
+        <v>-15900</v>
       </c>
       <c r="J81" s="3">
-        <v>-33700</v>
+        <v>-17400</v>
       </c>
       <c r="K81" s="3">
         <v>-5900</v>
@@ -3102,25 +3102,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>19700</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
-        <v>12700</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>7200</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>4300</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>3100</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
@@ -3318,25 +3318,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>17700</v>
+        <v>13000</v>
       </c>
       <c r="E89" s="3">
-        <v>8700</v>
+        <v>6100</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G89" s="3">
-        <v>9400</v>
+        <v>7600</v>
       </c>
       <c r="H89" s="3">
-        <v>-2600</v>
+        <v>-1900</v>
       </c>
       <c r="I89" s="3">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="J89" s="3">
-        <v>-10200</v>
+        <v>-5300</v>
       </c>
       <c r="K89" s="3">
         <v>-2200</v>
@@ -3370,25 +3370,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
-        <v>-800</v>
+        <v>-600</v>
       </c>
       <c r="F91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-300</v>
       </c>
       <c r="H91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>5</v>
@@ -3478,25 +3478,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-14600</v>
+        <v>-10700</v>
       </c>
       <c r="E94" s="3">
-        <v>-25400</v>
+        <v>-18000</v>
       </c>
       <c r="F94" s="3">
-        <v>-35900</v>
+        <v>-27200</v>
       </c>
       <c r="G94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-4200</v>
       </c>
-      <c r="H94" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-5600</v>
-      </c>
       <c r="J94" s="3">
-        <v>3100</v>
+        <v>1600</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -3674,25 +3674,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-6300</v>
+        <v>-4600</v>
       </c>
       <c r="E100" s="3">
-        <v>10500</v>
+        <v>7400</v>
       </c>
       <c r="F100" s="3">
-        <v>18700</v>
+        <v>14100</v>
       </c>
       <c r="G100" s="3">
-        <v>33500</v>
+        <v>27200</v>
       </c>
       <c r="H100" s="3">
-        <v>-800</v>
+        <v>-600</v>
       </c>
       <c r="I100" s="3">
-        <v>12500</v>
+        <v>11400</v>
       </c>
       <c r="J100" s="3">
-        <v>10600</v>
+        <v>5500</v>
       </c>
       <c r="K100" s="3">
         <v>6100</v>
@@ -3710,25 +3710,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
-        <v>-900</v>
-      </c>
       <c r="F101" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="G101" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="H101" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="I101" s="3">
-        <v>-900</v>
+        <v>-700</v>
       </c>
       <c r="J101" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K101" s="3">
         <v>-200</v>
@@ -3746,25 +3746,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3700</v>
+        <v>-2800</v>
       </c>
       <c r="E102" s="3">
-        <v>-7100</v>
+        <v>-5000</v>
       </c>
       <c r="F102" s="3">
-        <v>-15200</v>
+        <v>-11500</v>
       </c>
       <c r="G102" s="3">
-        <v>38200</v>
+        <v>31100</v>
       </c>
       <c r="H102" s="3">
-        <v>-7200</v>
+        <v>-5400</v>
       </c>
       <c r="I102" s="3">
-        <v>5400</v>
+        <v>6100</v>
       </c>
       <c r="J102" s="3">
-        <v>3900</v>
+        <v>2000</v>
       </c>
       <c r="K102" s="3">
         <v>3600</v>

--- a/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>BRAG</t>
   </si>
@@ -656,173 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42766</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42400</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42035</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>105600</v>
+      </c>
+      <c r="E8" s="3">
         <v>103400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>90600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>66300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>56800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>29800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2700</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E9" s="3">
         <v>48200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>34100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>32100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4400</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E10" s="3">
         <v>55200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>48200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>32200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,44 +849,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
         <v>6300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
+      <c r="J12" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>900</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1700</v>
       </c>
       <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,81 +924,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1600</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E15" s="3">
         <v>14400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2300</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>600</v>
       </c>
       <c r="M15" s="3">
+        <v>600</v>
+      </c>
+      <c r="N15" s="3">
         <v>500</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,80 +1019,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>109500</v>
+      </c>
+      <c r="E17" s="3">
         <v>104300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>91400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>72000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>57300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8500</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5800</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,29 +1114,30 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1112,14 +1145,17 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1127,133 +1163,142 @@
         <v>13500</v>
       </c>
       <c r="E21" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F21" s="3">
         <v>8100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5400</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5900</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1261,9 +1306,12 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,81 +1345,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5900</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5900</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1462,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1421,19 +1481,19 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-1800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-10400</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>5</v>
@@ -1441,9 +1501,12 @@
       <c r="M29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1540,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,30 +1579,33 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -1544,50 +1613,56 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5900</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,86 +1696,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5900</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42766</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42400</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42035</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1799,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,49 +1816,53 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E41" s="3">
         <v>9700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>31900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>500</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
@@ -1782,7 +1871,7 @@
         <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -1802,45 +1891,51 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E43" s="3">
         <v>20600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1865,8 +1960,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1874,81 +1969,90 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
       </c>
       <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E46" s="3">
         <v>32200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>30700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>45000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>900</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1982,81 +2086,90 @@
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E49" s="3">
         <v>66000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>70600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>58900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>38800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>37400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>40300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2800</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2203,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,33 +2242,36 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
         <v>400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2162,9 +2281,12 @@
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,45 +2320,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E54" s="3">
         <v>114300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>111600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>94800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>88200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3700</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2379,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,55 +2396,59 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E57" s="3">
         <v>8300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
@@ -2324,119 +2457,128 @@
         <v>200</v>
       </c>
       <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2000</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
         <v>3600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E60" s="3">
         <v>30800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>36700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2446,33 +2588,36 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>200</v>
       </c>
       <c r="G62" s="3">
         <v>200</v>
       </c>
       <c r="H62" s="3">
+        <v>200</v>
+      </c>
+      <c r="I62" s="3">
         <v>16000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
@@ -2482,9 +2627,12 @@
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2666,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2705,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,45 +2744,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E66" s="3">
         <v>36600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2803,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2839,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,9 +2878,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2750,9 +2917,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,9 +2956,12 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2796,35 +2969,38 @@
         <v>-84100</v>
       </c>
       <c r="E72" s="3">
+        <v>-84100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-77200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-78200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-74900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-52400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-39700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-25700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-34300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-31100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-25700</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3034,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3073,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,45 +3112,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E76" s="3">
         <v>77600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>74300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>75300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>500</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,86 +3190,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42766</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42400</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42035</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5900</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,44 +3293,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>600</v>
       </c>
       <c r="M83" s="3">
+        <v>600</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3368,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3407,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3446,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3485,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,45 +3524,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E89" s="3">
         <v>13000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,25 +3583,26 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -3390,8 +3610,8 @@
       <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>5</v>
+      <c r="K91" s="3">
+        <v>-100</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>5</v>
@@ -3399,9 +3619,12 @@
       <c r="M91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3658,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,45 +3697,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1600</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,8 +3756,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3559,9 +3792,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3831,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3870,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,115 +3909,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>14100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>11400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>31100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>BRAG</t>
   </si>
@@ -855,8 +855,8 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
+      <c r="D12" s="3">
+        <v>9300</v>
       </c>
       <c r="E12" s="3">
         <v>6300</v>
@@ -934,7 +934,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-300</v>
+        <v>300</v>
       </c>
       <c r="E14" s="3">
         <v>300</v>
@@ -1026,7 +1026,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>109500</v>
+        <v>109300</v>
       </c>
       <c r="E17" s="3">
         <v>104300</v>
@@ -1065,7 +1065,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3900</v>
+        <v>-3700</v>
       </c>
       <c r="E18" s="3">
         <v>-1000</v>
@@ -1121,7 +1121,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13500</v>
+        <v>13300</v>
       </c>
       <c r="E21" s="3">
         <v>13500</v>
@@ -1199,7 +1199,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3300</v>
+        <v>2400</v>
       </c>
       <c r="E22" s="3">
         <v>2000</v>
@@ -1589,7 +1589,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>-500</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1862,7 +1862,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
         <v>100</v>
@@ -1978,8 +1978,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>1200</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
@@ -2135,7 +2135,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>71000</v>
+        <v>57600</v>
       </c>
       <c r="E49" s="3">
         <v>66000</v>
@@ -2403,7 +2403,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>20700</v>
+        <v>3400</v>
       </c>
       <c r="E57" s="3">
         <v>8300</v>
@@ -3300,7 +3300,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>17500</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
         <v>1000</v>

--- a/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BRAG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>BRAG</t>
   </si>
@@ -656,185 +656,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42766</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42400</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42035</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E8" s="3">
         <v>105600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>103400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>90600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>66300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>56800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>29800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2700</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E9" s="3">
         <v>49600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>48200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>42400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>34100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>32100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4400</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E10" s="3">
         <v>56000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>55200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>48200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>32200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,47 +862,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E12" s="3">
         <v>9300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
+      <c r="K12" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1700</v>
       </c>
       <c r="N12" s="3">
         <v>1700</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,87 +943,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
-        <v>300</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1600</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E15" s="3">
         <v>17500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2300</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>600</v>
       </c>
       <c r="M15" s="3">
         <v>600</v>
       </c>
       <c r="N15" s="3">
+        <v>600</v>
+      </c>
+      <c r="O15" s="3">
         <v>500</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1020,86 +1045,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E17" s="3">
         <v>109300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>104300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>91400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>72000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>57300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8500</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5800</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,32 +1147,33 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1148,160 +1181,172 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E21" s="3">
         <v>13300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5400</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5900</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1309,9 +1354,12 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1348,87 +1396,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5900</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5900</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1465,9 +1522,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1484,19 +1544,19 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-1800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-10400</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>5</v>
@@ -1504,9 +1564,12 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1543,9 +1606,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1582,33 +1648,36 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -1616,53 +1685,59 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5900</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1699,92 +1774,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5900</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42766</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42400</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42035</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1800,8 +1884,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1817,55 +1902,59 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E41" s="3">
         <v>10800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>18200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>500</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>100</v>
@@ -1874,7 +1963,7 @@
         <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1894,48 +1983,54 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E43" s="3">
         <v>20800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1963,8 +2058,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -1972,92 +2067,101 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
       </c>
       <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E46" s="3">
         <v>34300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>30700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>900</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>500</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>5</v>
@@ -2089,48 +2193,54 @@
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2138,38 +2248,41 @@
         <v>57600</v>
       </c>
       <c r="E49" s="3">
+        <v>57600</v>
+      </c>
+      <c r="F49" s="3">
         <v>66000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>70600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>58900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>38800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>37400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>40300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2800</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2206,9 +2319,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2245,36 +2361,39 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>500</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2284,9 +2403,12 @@
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2323,48 +2445,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E54" s="3">
         <v>110400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>114300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>111600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>94800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>88200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>49200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>51800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3700</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2380,8 +2508,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2397,61 +2526,65 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E58" s="3">
         <v>7700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
@@ -2460,128 +2593,137 @@
         <v>200</v>
       </c>
       <c r="J58" s="3">
+        <v>200</v>
+      </c>
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2000</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E60" s="3">
         <v>30100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2591,36 +2733,39 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
       </c>
       <c r="H62" s="3">
         <v>200</v>
       </c>
       <c r="I62" s="3">
+        <v>200</v>
+      </c>
+      <c r="J62" s="3">
         <v>16000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19800</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
@@ -2630,9 +2775,12 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2669,9 +2817,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2708,9 +2859,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2747,48 +2901,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E66" s="3">
         <v>34300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>37200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3200</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2804,8 +2964,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2842,9 +3003,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2881,9 +3045,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2920,9 +3087,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2959,48 +3129,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-84100</v>
+        <v>-105000</v>
       </c>
       <c r="E72" s="3">
         <v>-84100</v>
       </c>
       <c r="F72" s="3">
+        <v>-84100</v>
+      </c>
+      <c r="G72" s="3">
         <v>-77200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-78200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-74900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-52400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-39700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-25700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-34300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-31100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25700</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3037,9 +3213,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3076,9 +3255,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3115,48 +3297,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E76" s="3">
         <v>76100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>77600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>75300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>48800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>500</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3193,92 +3381,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42766</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42400</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42035</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5900</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3294,47 +3491,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>600</v>
       </c>
       <c r="N83" s="3">
+        <v>600</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3371,9 +3572,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3410,9 +3614,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3449,9 +3656,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3488,9 +3698,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3527,48 +3740,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E89" s="3">
         <v>11600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3584,28 +3803,29 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -3613,8 +3833,8 @@
       <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
+      <c r="L91" s="3">
+        <v>-100</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>5</v>
@@ -3622,9 +3842,12 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3661,9 +3884,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3700,48 +3926,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1600</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3757,8 +3989,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3795,9 +4028,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3834,9 +4070,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3873,9 +4112,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3912,124 +4154,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E100" s="3">
         <v>3700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>7400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>14100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>27200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>11400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>31100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
